--- a/Письма заказчику/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).xlsx
+++ b/Письма заказчику/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Projects\380-25_Ivanovo_TEC\Письма заказчику\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin.DESKTOP-JV0Q39O\Documents\GitHub\380-25_Ivanovo_TEC\Письма заказчику\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F237039-4743-40BE-AAC3-17D6A811BDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="ОТР-ПД-РД" sheetId="1" r:id="rId1"/>
@@ -123,17 +122,16 @@
     <definedName name="Статус1">'ОТР-ПД-РД'!$B$130:$C$132</definedName>
     <definedName name="Статус2">'ОТР-ПД-РД'!$B$135:$C$136</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <customWorkbookViews>
+    <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
+    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
+    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
+    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
+    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
     <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
-    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
-    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
   </customWorkbookViews>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -154,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="261">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -1277,11 +1275,17 @@
   <si>
     <t>Отсутствует маркировка кабельных связей в системе ККС</t>
   </si>
+  <si>
+    <t>Отмаркировано в соответствии с исходными данными</t>
+  </si>
+  <si>
+    <t>Замечание снято ранее</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1456,7 +1460,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1490,6 +1494,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1625,7 +1635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1901,17 +1911,11 @@
     <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1925,17 +1929,38 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1964,47 +1989,24 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2" xfId="1"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2118,6 +2120,20 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2252,20 +2268,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="B130:B134" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="B130:B134"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Столбец1" dataDxfId="8"/>
+    <tableColumn id="1" name="Столбец1" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="B21:B25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="B21:B25"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Столбец1" dataDxfId="2"/>
+    <tableColumn id="1" name="Столбец1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2567,7 +2583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2629,13 +2645,13 @@
       <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -2657,13 +2673,13 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="30"/>
@@ -2685,12 +2701,12 @@
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
       <c r="E4" s="48"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -2713,12 +2729,12 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
       <c r="E5" s="48"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -2795,44 +2811,44 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:256" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="94" t="s">
+      <c r="D8" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="94" t="s">
+      <c r="F8" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="94" t="s">
+      <c r="G8" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="94" t="s">
+      <c r="H8" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="95" t="s">
+      <c r="I8" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="94" t="s">
+      <c r="J8" s="102"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="94"/>
-      <c r="N8" s="95" t="s">
+      <c r="M8" s="99"/>
+      <c r="N8" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="95"/>
-      <c r="P8" s="98" t="s">
+      <c r="O8" s="102"/>
+      <c r="P8" s="96" t="s">
         <v>46</v>
       </c>
       <c r="Q8" s="34" t="s">
@@ -2857,14 +2873,14 @@
       </c>
     </row>
     <row r="9" spans="1:256" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="100"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
       <c r="I9" s="25" t="s">
         <v>29</v>
       </c>
@@ -2886,7 +2902,7 @@
       <c r="O9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="99"/>
+      <c r="P9" s="97"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
         <v>6</v>
@@ -2907,29 +2923,29 @@
       </c>
     </row>
     <row r="10" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="104" t="s">
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="103" t="s">
+      <c r="J10" s="93"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="103"/>
-      <c r="N10" s="104" t="s">
+      <c r="M10" s="94"/>
+      <c r="N10" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="104"/>
+      <c r="O10" s="93"/>
       <c r="P10" s="47" t="s">
         <v>17</v>
       </c>
@@ -3764,7 +3780,7 @@
       <c r="IU13" s="40"/>
       <c r="IV13" s="40"/>
     </row>
-    <row r="14" spans="1:256" s="37" customFormat="1" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:256" s="37" customFormat="1" ht="128.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>3</v>
       </c>
@@ -7694,7 +7710,7 @@
       <c r="I28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="101" t="s">
+      <c r="J28" s="100" t="s">
         <v>106</v>
       </c>
       <c r="K28" s="43" t="s">
@@ -7974,7 +7990,7 @@
       <c r="I29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="102"/>
+      <c r="J29" s="101"/>
       <c r="K29" s="43" t="s">
         <v>103</v>
       </c>
@@ -9628,7 +9644,7 @@
       <c r="I35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="101"/>
+      <c r="J35" s="100"/>
       <c r="K35" s="43" t="s">
         <v>103</v>
       </c>
@@ -9902,7 +9918,7 @@
       <c r="I36" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="102"/>
+      <c r="J36" s="101"/>
       <c r="K36" s="43" t="s">
         <v>103</v>
       </c>
@@ -10429,29 +10445,29 @@
       <c r="IV37" s="40"/>
     </row>
     <row r="38" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="103" t="s">
+      <c r="A38" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="104" t="s">
+      <c r="B38" s="94"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="94"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="103" t="s">
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="103"/>
-      <c r="N38" s="104" t="s">
+      <c r="M38" s="94"/>
+      <c r="N38" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="O38" s="104"/>
+      <c r="O38" s="93"/>
       <c r="P38" s="47" t="s">
         <v>17</v>
       </c>
@@ -14234,7 +14250,7 @@
       <c r="IU51" s="40"/>
       <c r="IV51" s="40"/>
     </row>
-    <row r="52" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>14</v>
       </c>
@@ -14255,7 +14271,9 @@
       <c r="H52" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I52" s="17"/>
+      <c r="I52" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J52" s="77"/>
       <c r="K52" s="43"/>
       <c r="L52" s="16"/>
@@ -14504,14 +14522,14 @@
       <c r="IU52" s="40"/>
       <c r="IV52" s="40"/>
     </row>
-    <row r="53" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>15</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="121" t="s">
         <v>140</v>
       </c>
       <c r="D53" s="6"/>
@@ -14525,8 +14543,12 @@
       <c r="H53" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I53" s="17"/>
-      <c r="J53" s="77"/>
+      <c r="I53" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" s="77" t="s">
+        <v>259</v>
+      </c>
       <c r="K53" s="43"/>
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
@@ -14774,7 +14796,7 @@
       <c r="IU53" s="40"/>
       <c r="IV53" s="40"/>
     </row>
-    <row r="54" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>16</v>
       </c>
@@ -14795,7 +14817,9 @@
       <c r="H54" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I54" s="17"/>
+      <c r="I54" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J54" s="77"/>
       <c r="K54" s="43"/>
       <c r="L54" s="16"/>
@@ -15044,7 +15068,7 @@
       <c r="IU54" s="40"/>
       <c r="IV54" s="40"/>
     </row>
-    <row r="55" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>17</v>
       </c>
@@ -15065,7 +15089,9 @@
       <c r="H55" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I55" s="17"/>
+      <c r="I55" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J55" s="77"/>
       <c r="K55" s="43"/>
       <c r="L55" s="16"/>
@@ -15314,7 +15340,7 @@
       <c r="IU55" s="40"/>
       <c r="IV55" s="40"/>
     </row>
-    <row r="56" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>18</v>
       </c>
@@ -15335,8 +15361,12 @@
       <c r="H56" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I56" s="17"/>
-      <c r="J56" s="77"/>
+      <c r="I56" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="77" t="s">
+        <v>260</v>
+      </c>
       <c r="K56" s="43"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
@@ -15584,7 +15614,7 @@
       <c r="IU56" s="40"/>
       <c r="IV56" s="40"/>
     </row>
-    <row r="57" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>19</v>
       </c>
@@ -15605,8 +15635,12 @@
       <c r="H57" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="77"/>
+      <c r="I57" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="77" t="s">
+        <v>260</v>
+      </c>
       <c r="K57" s="43"/>
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
@@ -15861,7 +15895,7 @@
       <c r="B58" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="92" t="s">
         <v>151</v>
       </c>
       <c r="D58" s="6"/>
@@ -16685,7 +16719,9 @@
       <c r="H61" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I61" s="17"/>
+      <c r="I61" s="17" t="s">
+        <v>18</v>
+      </c>
       <c r="J61" s="77"/>
       <c r="K61" s="43"/>
       <c r="L61" s="16"/>
@@ -18015,29 +18051,29 @@
       <c r="IV65" s="40"/>
     </row>
     <row r="66" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="103" t="s">
+      <c r="A66" s="94" t="s">
         <v>162</v>
       </c>
-      <c r="B66" s="103"/>
-      <c r="C66" s="103"/>
-      <c r="D66" s="103"/>
-      <c r="E66" s="103"/>
-      <c r="F66" s="103"/>
-      <c r="G66" s="103"/>
-      <c r="H66" s="103"/>
-      <c r="I66" s="104" t="s">
+      <c r="B66" s="94"/>
+      <c r="C66" s="94"/>
+      <c r="D66" s="94"/>
+      <c r="E66" s="94"/>
+      <c r="F66" s="94"/>
+      <c r="G66" s="94"/>
+      <c r="H66" s="94"/>
+      <c r="I66" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="104"/>
-      <c r="K66" s="104"/>
-      <c r="L66" s="103" t="s">
+      <c r="J66" s="93"/>
+      <c r="K66" s="93"/>
+      <c r="L66" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="M66" s="103"/>
-      <c r="N66" s="104" t="s">
+      <c r="M66" s="94"/>
+      <c r="N66" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="O66" s="104"/>
+      <c r="O66" s="93"/>
       <c r="P66" s="47" t="s">
         <v>17</v>
       </c>
@@ -21794,14 +21830,14 @@
       <c r="IU79" s="40"/>
       <c r="IV79" s="40"/>
     </row>
-    <row r="80" spans="1:256" s="37" customFormat="1" ht="322.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:256" s="37" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>14</v>
       </c>
       <c r="B80" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="C80" s="88" t="s">
+      <c r="C80" s="122" t="s">
         <v>181</v>
       </c>
       <c r="D80" s="84"/>
@@ -28004,7 +28040,7 @@
       <c r="IU102" s="40"/>
       <c r="IV102" s="40"/>
     </row>
-    <row r="103" spans="1:256" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="84"/>
       <c r="C103" s="88" t="s">
@@ -34787,10 +34823,10 @@
       <c r="J129" s="10"/>
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
-      <c r="M129" s="97" t="s">
+      <c r="M129" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="N129" s="97"/>
+      <c r="N129" s="95"/>
       <c r="O129" s="10"/>
       <c r="P129" s="11"/>
       <c r="Q129" s="11"/>
@@ -37932,25 +37968,47 @@
       <c r="E146" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:IV118" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A11:IV118"/>
   <customSheetViews>
-    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
-      <selection activeCell="C63" sqref="C63:D63"/>
+    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
+      <selection activeCell="F21" sqref="F21"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-      <autoFilter ref="B9:Y51" xr:uid="{F58F85A5-D4BC-43AD-A88E-A6025D5C6450}"/>
+      <autoFilter ref="B9:Y31"/>
     </customSheetView>
-    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
-      <selection activeCell="K12" sqref="K12"/>
+    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
+      <selection activeCell="K20" sqref="K20"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="B9:Y31" xr:uid="{A1F78223-B7B7-481D-BEE7-23E428C77E33}"/>
+      <autoFilter ref="B9:Y31"/>
+    </customSheetView>
+    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
+      <selection activeCell="K23" sqref="K23"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+      <autoFilter ref="B9:Y31"/>
+    </customSheetView>
+    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
+      <selection activeCell="C238" sqref="C238:D238"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
+      <autoFilter ref="B10:Z230">
+        <filterColumn colId="7">
+          <filters>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
+            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
     </customSheetView>
     <customSheetView guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" topLeftCell="K144">
       <selection activeCell="O76" sqref="O76"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId3"/>
-      <autoFilter ref="B10:Z230" xr:uid="{A32F797D-1603-48F1-A17B-B382C5562735}">
+      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId5"/>
+      <autoFilter ref="B10:Z230">
         <filterColumn colId="7">
           <filters>
             <filter val="ИГН, ГТЭП"/>
@@ -37966,48 +38024,29 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
-      <selection activeCell="C238" sqref="C238:D238"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="B10:Z230" xr:uid="{F8B46242-A4B7-4138-97E0-490DB93B93DE}">
-        <filterColumn colId="7">
-          <filters>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
-            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
-    </customSheetView>
-    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
-      <selection activeCell="K23" sqref="K23"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="B9:Y31" xr:uid="{1D197EA4-D367-431F-817D-FE7D6C75532B}"/>
-    </customSheetView>
-    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
-      <selection activeCell="K20" sqref="K20"/>
+    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
+      <selection activeCell="K12" sqref="K12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="B9:Y31" xr:uid="{8B4D6867-6AC5-4E57-9F60-9A41E9201C29}"/>
+      <autoFilter ref="B9:Y31"/>
     </customSheetView>
-    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
-      <selection activeCell="F21" sqref="F21"/>
+    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
+      <selection activeCell="C63" sqref="C63:D63"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId7"/>
-      <autoFilter ref="B9:Y31" xr:uid="{7BBA34B8-7D42-43D5-A115-F0059FE29F68}"/>
+      <autoFilter ref="B9:Y51"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="31">
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
     <mergeCell ref="M129:N129"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="A8:A9"/>
@@ -38024,25 +38063,22 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="L38:M38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127 I39:I65" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127 I39:I65">
       <formula1>$B$131:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65">
       <formula1>$B$135:$B$136</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65">
       <formula1>$B$138:$B$140</formula1>
     </dataValidation>
   </dataValidations>
@@ -38058,7 +38094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -38119,11 +38155,11 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -38146,12 +38182,12 @@
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -38173,11 +38209,11 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="48"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -38200,12 +38236,12 @@
       <c r="W4" s="3"/>
     </row>
     <row r="5" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -38282,36 +38318,36 @@
       <c r="A8" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="109" t="s">
+      <c r="B8" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="94" t="s">
+      <c r="D8" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="94" t="s">
+      <c r="F8" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="111" t="s">
+      <c r="G8" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="94" t="s">
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="94"/>
-      <c r="M8" s="95" t="s">
+      <c r="L8" s="99"/>
+      <c r="M8" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="95"/>
-      <c r="O8" s="98" t="s">
+      <c r="N8" s="102"/>
+      <c r="O8" s="96" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="34" t="s">
@@ -38337,21 +38373,21 @@
     </row>
     <row r="9" spans="1:255" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="120"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
       <c r="G9" s="25" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="111" t="s">
+      <c r="I9" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="112"/>
+      <c r="J9" s="117"/>
       <c r="K9" s="19" t="s">
         <v>8</v>
       </c>
@@ -38364,7 +38400,7 @@
       <c r="N9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="99"/>
+      <c r="O9" s="97"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35" t="s">
         <v>6</v>
@@ -38385,28 +38421,28 @@
       </c>
     </row>
     <row r="10" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A10" s="103" t="s">
+      <c r="A10" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="116" t="s">
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="103" t="s">
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="103"/>
-      <c r="M10" s="104" t="s">
+      <c r="L10" s="94"/>
+      <c r="M10" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="104"/>
+      <c r="N10" s="93"/>
       <c r="O10" s="47" t="s">
         <v>17</v>
       </c>
@@ -38430,8 +38466,8 @@
       <c r="F11" s="59"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="115"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
       <c r="K11" s="6"/>
       <c r="L11" s="16"/>
       <c r="M11" s="71"/>
@@ -38689,8 +38725,8 @@
       <c r="F12" s="59"/>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="115"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
       <c r="K12" s="6"/>
       <c r="L12" s="16"/>
       <c r="M12" s="71"/>
@@ -38948,8 +38984,8 @@
       <c r="F13" s="59"/>
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
-      <c r="I13" s="114"/>
-      <c r="J13" s="115"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="109"/>
       <c r="K13" s="6"/>
       <c r="L13" s="16"/>
       <c r="M13" s="71"/>
@@ -39207,8 +39243,8 @@
       <c r="F14" s="59"/>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="115"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="109"/>
       <c r="K14" s="6"/>
       <c r="L14" s="16"/>
       <c r="M14" s="71"/>
@@ -39466,8 +39502,8 @@
       <c r="F15" s="59"/>
       <c r="G15" s="70"/>
       <c r="H15" s="70"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="115"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="109"/>
       <c r="K15" s="6"/>
       <c r="L15" s="16"/>
       <c r="M15" s="71"/>
@@ -39715,28 +39751,28 @@
       <c r="IU15" s="40"/>
     </row>
     <row r="16" spans="1:255" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="116" t="s">
+      <c r="B16" s="112"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="103" t="s">
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="103"/>
-      <c r="M16" s="104" t="s">
+      <c r="L16" s="94"/>
+      <c r="M16" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="104"/>
+      <c r="N16" s="93"/>
       <c r="O16" s="47" t="s">
         <v>17</v>
       </c>
@@ -39994,8 +40030,8 @@
       <c r="F17" s="59"/>
       <c r="G17" s="70"/>
       <c r="H17" s="70"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="115"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
       <c r="K17" s="6"/>
       <c r="L17" s="16"/>
       <c r="M17" s="71"/>
@@ -40253,8 +40289,8 @@
       <c r="F18" s="59"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="115"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="109"/>
       <c r="K18" s="6"/>
       <c r="L18" s="16"/>
       <c r="M18" s="71"/>
@@ -40763,18 +40799,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="63"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
       <c r="E20" s="7"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="97" t="s">
+      <c r="K20" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="97"/>
+      <c r="L20" s="95"/>
       <c r="M20" s="23"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
@@ -41032,8 +41068,8 @@
       <c r="H21" s="10"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="97"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
       <c r="M21" s="23"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
@@ -43388,25 +43424,8 @@
       <c r="D33" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="K1:K33" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="K1:K33"/>
   <mergeCells count="33">
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B8:B9"/>
@@ -43423,28 +43442,45 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:K15">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17:K19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18">
       <formula1>$B$22:$B$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18">
       <formula1>$B$29:$B$31</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18">
       <formula1>$B$26:$B$27</formula1>
     </dataValidation>
   </dataValidations>

--- a/Письма заказчику/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).xlsx
+++ b/Письма заказчику/Ведомость проверки результатов РД АСУ ТП 10.10.2025 (50495598 v1).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin.DESKTOP-JV0Q39O\Documents\GitHub\380-25_Ivanovo_TEC\Письма заказчику\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Projects\380-25_Ivanovo_TEC\Письма заказчику\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B7E772-E67B-4E7C-8F5C-9A37C74AA183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОТР-ПД-РД" sheetId="1" r:id="rId1"/>
@@ -122,15 +123,15 @@
     <definedName name="Статус1">'ОТР-ПД-РД'!$B$130:$C$132</definedName>
     <definedName name="Статус2">'ОТР-ПД-РД'!$B$135:$C$136</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
+    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
+    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
     <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
-    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
-    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
-    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -152,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="278">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -865,11 +866,6 @@
     <t>Пункт 1.8</t>
   </si>
   <si>
-    <t>Стадия 4 - указать части эскизного проекта.
-Стадия 5 - указать части технического проекта.
-Стадия 5 - указать части рабочей документации.</t>
-  </si>
-  <si>
     <t>Лист 3, 15, 16, 24, 25, 28: Оборудование в системе KKS отмаркировано не полностью</t>
   </si>
   <si>
@@ -1281,11 +1277,68 @@
   <si>
     <t>Замечание снято ранее</t>
   </si>
+  <si>
+    <t>Отдельных шкафов питания не предусмотрено. Заказываются шкафы DKC по спецификации.</t>
+  </si>
+  <si>
+    <t>Перечень элементов указан в правом верхнем углу чертежей шкафов</t>
+  </si>
+  <si>
+    <t>Для разработки раздела ИБ заключается договор с другой организацией.</t>
+  </si>
+  <si>
+    <t>Всё оборудование подбиралось без опросных листов.</t>
+  </si>
+  <si>
+    <t>Высылалось ранее</t>
+  </si>
+  <si>
+    <t>Отражены в разделе АСУ ТП.СБ.2 "Схемы принципиальные управления"</t>
+  </si>
+  <si>
+    <t>Разработка фундаментных рам и закладных элементов для монтажа шкафов и пультов в составе раздела АСУТП не предусмотрена.
+В рамках раздела АСУТП представлена схема (план) расположения шкафов, см. раздел 878.2023-АСУ ТП.С7 "План расположения оборудования", предназначенная для использования в качестве исходных данных разработчиком монтажных (строительных) конструкций.</t>
+  </si>
+  <si>
+    <t>Изменён ККС принтера</t>
+  </si>
+  <si>
+    <t>Схема ЛВС отражена в разделе 878.2023-АСУ ТП.Г1  "Структурная схема цифрового обмена с адресацией цифровых сетей". Система организации единого времени отражена в разделе 878.2023-АСУ ТП.СЕВ "Система единого времени"</t>
+  </si>
+  <si>
+    <t>Отражено в разделе 878.2023-АСУ ТП.СП "Схемы программно-алгоритмические расчётных задач, контроля, управления, автоматического регулирования, сигнализаций и блокировок"</t>
+  </si>
+  <si>
+    <t>Стадия 4 - указать части эскизного проекта.
+Стадия 5 - указать части технического проекта.
+Стадия 6 - указать части рабочей документации.</t>
+  </si>
+  <si>
+    <t>В спецификации кабеля учтены</t>
+  </si>
+  <si>
+    <t>Количество модулей ввода/вывод в спецификации соответствует требованию по резервированию.</t>
+  </si>
+  <si>
+    <t>В описании добавлено указание учесть резерв не менее 10% для каждого типа сигналов. После перечня входных данных добавлен перечень резервных каналов</t>
+  </si>
+  <si>
+    <t>Организация коммерческих узлов учета электроэнергии, тепла и газа и сбор данных в систему АСУ ТП не относится и не входит в документацию по АСУ ТП Водогрейной котельной. В перечне сигналов АСУ ТП Водогрейной котельной предусмотрены сигналы с узлов учета. Сами же узлы учета будут разработаны как отдельные разделы рабочей документации с уточнением какие именно параметры будут передаваться в АСУ ТП ВК.</t>
+  </si>
+  <si>
+    <t>Кабельные связи с узлами учета должны быть учтены в рабочей документации по организации узлов учёта.</t>
+  </si>
+  <si>
+    <t>Отдельных шкафов питания в составе АСУТП не предусмотрено.</t>
+  </si>
+  <si>
+    <t>В связи с большим размером документа и  сильному падению производительности при разработке, для данных замечаний разработан отдельный документ "Таблица сигналов"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1504,7 +1557,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1630,12 +1683,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1865,9 +1929,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1877,20 +1938,11 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1911,11 +1963,38 @@
     <xf numFmtId="49" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1929,38 +2008,17 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1989,24 +2047,53 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2120,20 +2207,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2268,20 +2341,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="B130:B134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица3" displayName="Таблица3" ref="B130:B134" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="B130:B134" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Столбец1" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Столбец1" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="B21:B25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица36" displayName="Таблица36" ref="B21:B25" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="B21:B25" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Столбец1" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Столбец1" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2583,7 +2656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2597,7 +2670,7 @@
     <col min="5" max="5" width="112.85546875" style="5" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" style="5" customWidth="1"/>
     <col min="7" max="8" width="26.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" style="14" customWidth="1"/>
     <col min="11" max="11" width="18.140625" style="5" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
@@ -2645,13 +2718,13 @@
       <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -2673,13 +2746,13 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="30"/>
@@ -2701,12 +2774,12 @@
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
       <c r="E4" s="48"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -2729,12 +2802,12 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="48"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -2811,44 +2884,44 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:256" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
+      <c r="A8" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="99" t="s">
+      <c r="D8" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="99" t="s">
+      <c r="F8" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="99" t="s">
+      <c r="G8" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="99" t="s">
+      <c r="H8" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="102" t="s">
+      <c r="I8" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="99" t="s">
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="99"/>
-      <c r="N8" s="102" t="s">
+      <c r="M8" s="97"/>
+      <c r="N8" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="102"/>
-      <c r="P8" s="96" t="s">
+      <c r="O8" s="98"/>
+      <c r="P8" s="101" t="s">
         <v>46</v>
       </c>
       <c r="Q8" s="34" t="s">
@@ -2873,14 +2946,14 @@
       </c>
     </row>
     <row r="9" spans="1:256" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
+      <c r="A9" s="103"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
       <c r="I9" s="25" t="s">
         <v>29</v>
       </c>
@@ -2902,7 +2975,7 @@
       <c r="O9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="97"/>
+      <c r="P9" s="102"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
         <v>6</v>
@@ -2923,29 +2996,29 @@
       </c>
     </row>
     <row r="10" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="93" t="s">
+      <c r="B10" s="106"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="94" t="s">
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="94"/>
-      <c r="N10" s="93" t="s">
+      <c r="M10" s="106"/>
+      <c r="N10" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="93"/>
+      <c r="O10" s="107"/>
       <c r="P10" s="47" t="s">
         <v>17</v>
       </c>
@@ -3536,7 +3609,7 @@
         <v>19</v>
       </c>
       <c r="O13" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="38"/>
@@ -3780,7 +3853,7 @@
       <c r="IU13" s="40"/>
       <c r="IV13" s="40"/>
     </row>
-    <row r="14" spans="1:256" s="37" customFormat="1" ht="128.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:256" s="37" customFormat="1" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>3</v>
       </c>
@@ -3814,13 +3887,13 @@
         <v>21</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N14" s="16" t="s">
         <v>19</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="38"/>
@@ -5452,7 +5525,7 @@
       <c r="IU19" s="40"/>
       <c r="IV19" s="40"/>
     </row>
-    <row r="20" spans="1:256" s="37" customFormat="1" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:256" s="37" customFormat="1" ht="327.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>9</v>
       </c>
@@ -6886,13 +6959,13 @@
         <v>23</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N25" s="16" t="s">
         <v>33</v>
       </c>
       <c r="O25" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="38"/>
@@ -7710,7 +7783,7 @@
       <c r="I28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="100" t="s">
+      <c r="J28" s="104" t="s">
         <v>106</v>
       </c>
       <c r="K28" s="43" t="s">
@@ -7990,7 +8063,7 @@
       <c r="I29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="101"/>
+      <c r="J29" s="105"/>
       <c r="K29" s="43" t="s">
         <v>103</v>
       </c>
@@ -8247,7 +8320,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="6"/>
-      <c r="C30" s="92" t="s">
+      <c r="C30" s="88" t="s">
         <v>94</v>
       </c>
       <c r="D30" s="6"/>
@@ -9644,7 +9717,7 @@
       <c r="I35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="100"/>
+      <c r="J35" s="104"/>
       <c r="K35" s="43" t="s">
         <v>103</v>
       </c>
@@ -9918,7 +9991,7 @@
       <c r="I36" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="101"/>
+      <c r="J36" s="105"/>
       <c r="K36" s="43" t="s">
         <v>103</v>
       </c>
@@ -10445,29 +10518,29 @@
       <c r="IV37" s="40"/>
     </row>
     <row r="38" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
+      <c r="A38" s="106" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="94"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="94"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="93" t="s">
+      <c r="B38" s="106"/>
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="94" t="s">
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="94"/>
-      <c r="N38" s="93" t="s">
+      <c r="M38" s="106"/>
+      <c r="N38" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="O38" s="93"/>
+      <c r="O38" s="107"/>
       <c r="P38" s="47" t="s">
         <v>17</v>
       </c>
@@ -10719,7 +10792,7 @@
       <c r="B39" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="92" t="s">
+      <c r="C39" s="88" t="s">
         <v>116</v>
       </c>
       <c r="D39" s="6"/>
@@ -11807,7 +11880,7 @@
       <c r="B43" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="88" t="s">
         <v>120</v>
       </c>
       <c r="D43" s="6"/>
@@ -11825,7 +11898,7 @@
         <v>19</v>
       </c>
       <c r="J43" s="77" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K43" s="43"/>
       <c r="L43" s="16"/>
@@ -12099,7 +12172,7 @@
         <v>19</v>
       </c>
       <c r="J44" s="77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K44" s="43"/>
       <c r="L44" s="16"/>
@@ -13715,7 +13788,7 @@
       <c r="B50" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="92" t="s">
+      <c r="C50" s="88" t="s">
         <v>137</v>
       </c>
       <c r="D50" s="6"/>
@@ -14529,12 +14602,12 @@
       <c r="B53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="121" t="s">
+      <c r="C53" s="89" t="s">
         <v>140</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F53" s="46"/>
       <c r="G53" s="41" t="s">
@@ -14547,7 +14620,7 @@
         <v>19</v>
       </c>
       <c r="J53" s="77" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K53" s="43"/>
       <c r="L53" s="16"/>
@@ -15365,7 +15438,7 @@
         <v>18</v>
       </c>
       <c r="J56" s="77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K56" s="43"/>
       <c r="L56" s="16"/>
@@ -15639,7 +15712,7 @@
         <v>18</v>
       </c>
       <c r="J57" s="77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K57" s="43"/>
       <c r="L57" s="16"/>
@@ -15888,14 +15961,14 @@
       <c r="IU57" s="40"/>
       <c r="IV57" s="40"/>
     </row>
-    <row r="58" spans="1:256" s="37" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>20</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="92" t="s">
+      <c r="C58" s="88" t="s">
         <v>151</v>
       </c>
       <c r="D58" s="6"/>
@@ -16179,7 +16252,9 @@
       <c r="H59" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I59" s="17"/>
+      <c r="I59" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J59" s="77"/>
       <c r="K59" s="43"/>
       <c r="L59" s="16"/>
@@ -16449,8 +16524,12 @@
       <c r="H60" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="77"/>
+      <c r="I60" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="77" t="s">
+        <v>264</v>
+      </c>
       <c r="K60" s="43"/>
       <c r="L60" s="16"/>
       <c r="M60" s="16"/>
@@ -16722,7 +16801,9 @@
       <c r="I61" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J61" s="77"/>
+      <c r="J61" s="77" t="s">
+        <v>263</v>
+      </c>
       <c r="K61" s="43"/>
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
@@ -16991,8 +17072,12 @@
       <c r="H62" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I62" s="17"/>
-      <c r="J62" s="77"/>
+      <c r="I62" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="77" t="s">
+        <v>265</v>
+      </c>
       <c r="K62" s="43"/>
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
@@ -17245,7 +17330,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="6"/>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="88" t="s">
         <v>159</v>
       </c>
       <c r="D63" s="6"/>
@@ -17510,7 +17595,7 @@
       <c r="IU63" s="40"/>
       <c r="IV63" s="40"/>
     </row>
-    <row r="64" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:256" s="37" customFormat="1" ht="199.5" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>26</v>
       </c>
@@ -17531,8 +17616,12 @@
       <c r="H64" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I64" s="17"/>
-      <c r="J64" s="77"/>
+      <c r="I64" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="77" t="s">
+        <v>268</v>
+      </c>
       <c r="K64" s="43"/>
       <c r="L64" s="16"/>
       <c r="M64" s="16"/>
@@ -17780,12 +17869,12 @@
       <c r="IU64" s="40"/>
       <c r="IV64" s="40"/>
     </row>
-    <row r="65" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:256" s="37" customFormat="1" ht="156.75" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>27</v>
       </c>
       <c r="B65" s="6"/>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="89" t="s">
         <v>161</v>
       </c>
       <c r="D65" s="6"/>
@@ -17801,8 +17890,12 @@
       <c r="H65" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="17"/>
-      <c r="J65" s="77"/>
+      <c r="I65" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="77" t="s">
+        <v>269</v>
+      </c>
       <c r="K65" s="43"/>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
@@ -18051,29 +18144,29 @@
       <c r="IV65" s="40"/>
     </row>
     <row r="66" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="94" t="s">
+      <c r="A66" s="106" t="s">
         <v>162</v>
       </c>
-      <c r="B66" s="94"/>
-      <c r="C66" s="94"/>
-      <c r="D66" s="94"/>
-      <c r="E66" s="94"/>
-      <c r="F66" s="94"/>
-      <c r="G66" s="94"/>
-      <c r="H66" s="94"/>
-      <c r="I66" s="93" t="s">
+      <c r="B66" s="106"/>
+      <c r="C66" s="106"/>
+      <c r="D66" s="106"/>
+      <c r="E66" s="106"/>
+      <c r="F66" s="106"/>
+      <c r="G66" s="106"/>
+      <c r="H66" s="106"/>
+      <c r="I66" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="93"/>
-      <c r="K66" s="93"/>
-      <c r="L66" s="94" t="s">
+      <c r="J66" s="107"/>
+      <c r="K66" s="107"/>
+      <c r="L66" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="M66" s="94"/>
-      <c r="N66" s="93" t="s">
+      <c r="M66" s="106"/>
+      <c r="N66" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="O66" s="93"/>
+      <c r="O66" s="107"/>
       <c r="P66" s="47" t="s">
         <v>17</v>
       </c>
@@ -18322,14 +18415,14 @@
       <c r="A67" s="6">
         <v>1</v>
       </c>
-      <c r="B67" s="84" t="s">
+      <c r="B67" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="C67" s="88" t="s">
+      <c r="C67" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="D67" s="84"/>
-      <c r="E67" s="89" t="s">
+      <c r="D67" s="81"/>
+      <c r="E67" s="85" t="s">
         <v>163</v>
       </c>
       <c r="F67" s="46" t="s">
@@ -18590,21 +18683,21 @@
       <c r="IU67" s="40"/>
       <c r="IV67" s="40"/>
     </row>
-    <row r="68" spans="1:256" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>2</v>
       </c>
-      <c r="B68" s="84" t="s">
+      <c r="B68" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="C68" s="88" t="s">
+      <c r="C68" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="84" t="s">
+      <c r="D68" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="E68" s="89" t="s">
-        <v>168</v>
+      <c r="E68" s="85" t="s">
+        <v>270</v>
       </c>
       <c r="F68" s="46"/>
       <c r="G68" s="41" t="s">
@@ -18613,7 +18706,9 @@
       <c r="H68" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I68" s="17"/>
+      <c r="I68" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J68" s="77"/>
       <c r="K68" s="43"/>
       <c r="L68" s="16"/>
@@ -18862,20 +18957,20 @@
       <c r="IU68" s="40"/>
       <c r="IV68" s="40"/>
     </row>
-    <row r="69" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>3</v>
       </c>
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="C69" s="88" t="s">
+      <c r="C69" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="D69" s="84" t="s">
+      <c r="D69" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="E69" s="89" t="s">
+      <c r="E69" s="85" t="s">
         <v>107</v>
       </c>
       <c r="F69" s="46"/>
@@ -18885,8 +18980,12 @@
       <c r="H69" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I69" s="17"/>
-      <c r="J69" s="77"/>
+      <c r="I69" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="77" t="s">
+        <v>267</v>
+      </c>
       <c r="K69" s="43"/>
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
@@ -19134,22 +19233,22 @@
       <c r="IU69" s="40"/>
       <c r="IV69" s="40"/>
     </row>
-    <row r="70" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:256" s="37" customFormat="1" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>4</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="88" t="s">
+      <c r="C70" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="D70" s="84"/>
-      <c r="E70" s="89" t="s">
-        <v>171</v>
+      <c r="D70" s="81"/>
+      <c r="E70" s="85" t="s">
+        <v>170</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G70" s="41" t="s">
         <v>51</v>
@@ -19157,8 +19256,12 @@
       <c r="H70" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="77"/>
+      <c r="I70" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="77" t="s">
+        <v>273</v>
+      </c>
       <c r="K70" s="43"/>
       <c r="L70" s="16"/>
       <c r="M70" s="16"/>
@@ -19406,22 +19509,22 @@
       <c r="IU70" s="40"/>
       <c r="IV70" s="40"/>
     </row>
-    <row r="71" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:256" s="37" customFormat="1" ht="142.5" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>5</v>
       </c>
-      <c r="B71" s="84" t="s">
+      <c r="B71" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="88" t="s">
+      <c r="C71" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="D71" s="84"/>
-      <c r="E71" s="89" t="s">
-        <v>172</v>
+      <c r="D71" s="81"/>
+      <c r="E71" s="85" t="s">
+        <v>171</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G71" s="41" t="s">
         <v>51</v>
@@ -19429,8 +19532,12 @@
       <c r="H71" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I71" s="17"/>
-      <c r="J71" s="77"/>
+      <c r="I71" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="77" t="s">
+        <v>273</v>
+      </c>
       <c r="K71" s="43"/>
       <c r="L71" s="16"/>
       <c r="M71" s="16"/>
@@ -19682,15 +19789,15 @@
       <c r="A72" s="6">
         <v>6</v>
       </c>
-      <c r="B72" s="84" t="s">
+      <c r="B72" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="C72" s="88" t="s">
+      <c r="C72" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="84"/>
-      <c r="E72" s="89" t="s">
-        <v>174</v>
+      <c r="D72" s="81"/>
+      <c r="E72" s="85" t="s">
+        <v>173</v>
       </c>
       <c r="F72" s="46"/>
       <c r="G72" s="41" t="s">
@@ -19952,15 +20059,15 @@
       <c r="A73" s="6">
         <v>7</v>
       </c>
-      <c r="B73" s="84" t="s">
+      <c r="B73" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="C73" s="88" t="s">
+      <c r="C73" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="84"/>
-      <c r="E73" s="89" t="s">
-        <v>197</v>
+      <c r="D73" s="81"/>
+      <c r="E73" s="85" t="s">
+        <v>196</v>
       </c>
       <c r="F73" s="46"/>
       <c r="G73" s="41"/>
@@ -20218,15 +20325,15 @@
       <c r="A74" s="6">
         <v>8</v>
       </c>
-      <c r="B74" s="84" t="s">
+      <c r="B74" s="81" t="s">
+        <v>175</v>
+      </c>
+      <c r="C74" s="84" t="s">
+        <v>174</v>
+      </c>
+      <c r="D74" s="81"/>
+      <c r="E74" s="85" t="s">
         <v>176</v>
-      </c>
-      <c r="C74" s="88" t="s">
-        <v>175</v>
-      </c>
-      <c r="D74" s="84"/>
-      <c r="E74" s="89" t="s">
-        <v>177</v>
       </c>
       <c r="F74" s="46"/>
       <c r="G74" s="41" t="s">
@@ -20484,19 +20591,19 @@
       <c r="IU74" s="40"/>
       <c r="IV74" s="40"/>
     </row>
-    <row r="75" spans="1:256" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>9</v>
       </c>
-      <c r="B75" s="84" t="s">
+      <c r="B75" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="88" t="s">
+      <c r="C75" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="D75" s="84"/>
-      <c r="E75" s="89" t="s">
-        <v>182</v>
+      <c r="D75" s="81"/>
+      <c r="E75" s="85" t="s">
+        <v>181</v>
       </c>
       <c r="F75" s="46"/>
       <c r="G75" s="41" t="s">
@@ -20505,8 +20612,12 @@
       <c r="H75" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I75" s="17"/>
-      <c r="J75" s="77"/>
+      <c r="I75" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="77" t="s">
+        <v>272</v>
+      </c>
       <c r="K75" s="43"/>
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
@@ -20758,15 +20869,15 @@
       <c r="A76" s="6">
         <v>10</v>
       </c>
-      <c r="B76" s="84" t="s">
+      <c r="B76" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="C76" s="88" t="s">
+      <c r="C76" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="D76" s="84"/>
-      <c r="E76" s="89" t="s">
-        <v>195</v>
+      <c r="D76" s="81"/>
+      <c r="E76" s="85" t="s">
+        <v>194</v>
       </c>
       <c r="F76" s="46"/>
       <c r="G76" s="41"/>
@@ -21024,15 +21135,15 @@
       <c r="A77" s="6">
         <v>11</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B77" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C77" s="88" t="s">
+      <c r="C77" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="84"/>
-      <c r="E77" s="89" t="s">
-        <v>178</v>
+      <c r="D77" s="81"/>
+      <c r="E77" s="85" t="s">
+        <v>177</v>
       </c>
       <c r="F77" s="46"/>
       <c r="G77" s="41" t="s">
@@ -21290,19 +21401,19 @@
       <c r="IU77" s="40"/>
       <c r="IV77" s="40"/>
     </row>
-    <row r="78" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:256" s="37" customFormat="1" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>12</v>
       </c>
-      <c r="B78" s="84" t="s">
+      <c r="B78" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C78" s="88" t="s">
+      <c r="C78" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="D78" s="84"/>
-      <c r="E78" s="89" t="s">
-        <v>179</v>
+      <c r="D78" s="81"/>
+      <c r="E78" s="85" t="s">
+        <v>178</v>
       </c>
       <c r="F78" s="46"/>
       <c r="G78" s="41" t="s">
@@ -21311,8 +21422,12 @@
       <c r="H78" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I78" s="17"/>
-      <c r="J78" s="77"/>
+      <c r="I78" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="77" t="s">
+        <v>275</v>
+      </c>
       <c r="K78" s="43"/>
       <c r="L78" s="16"/>
       <c r="M78" s="16"/>
@@ -21560,19 +21675,19 @@
       <c r="IU78" s="40"/>
       <c r="IV78" s="40"/>
     </row>
-    <row r="79" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>13</v>
       </c>
-      <c r="B79" s="84" t="s">
+      <c r="B79" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C79" s="88" t="s">
+      <c r="C79" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="D79" s="84"/>
-      <c r="E79" s="89" t="s">
-        <v>198</v>
+      <c r="D79" s="81"/>
+      <c r="E79" s="85" t="s">
+        <v>197</v>
       </c>
       <c r="F79" s="46"/>
       <c r="G79" s="41" t="s">
@@ -21581,7 +21696,9 @@
       <c r="H79" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I79" s="17"/>
+      <c r="I79" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J79" s="77"/>
       <c r="K79" s="43"/>
       <c r="L79" s="16"/>
@@ -21834,15 +21951,15 @@
       <c r="A80" s="6">
         <v>14</v>
       </c>
-      <c r="B80" s="84" t="s">
+      <c r="B80" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="90" t="s">
         <v>180</v>
       </c>
-      <c r="C80" s="122" t="s">
-        <v>181</v>
-      </c>
-      <c r="D80" s="84"/>
-      <c r="E80" s="89" t="s">
-        <v>183</v>
+      <c r="D80" s="81"/>
+      <c r="E80" s="85" t="s">
+        <v>182</v>
       </c>
       <c r="F80" s="46"/>
       <c r="G80" s="41" t="s">
@@ -22104,15 +22221,15 @@
       <c r="A81" s="6">
         <v>15</v>
       </c>
-      <c r="B81" s="84" t="s">
+      <c r="B81" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="88" t="s">
+      <c r="C81" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D81" s="84"/>
-      <c r="E81" s="89" t="s">
-        <v>184</v>
+      <c r="D81" s="81"/>
+      <c r="E81" s="85" t="s">
+        <v>183</v>
       </c>
       <c r="F81" s="46"/>
       <c r="G81" s="41" t="s">
@@ -22370,19 +22487,19 @@
       <c r="IU81" s="40"/>
       <c r="IV81" s="40"/>
     </row>
-    <row r="82" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:256" s="37" customFormat="1" ht="85.5" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>16</v>
       </c>
-      <c r="B82" s="84" t="s">
+      <c r="B82" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C82" s="88" t="s">
+      <c r="C82" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D82" s="84"/>
-      <c r="E82" s="89" t="s">
-        <v>185</v>
+      <c r="D82" s="81"/>
+      <c r="E82" s="85" t="s">
+        <v>184</v>
       </c>
       <c r="F82" s="46"/>
       <c r="G82" s="41" t="s">
@@ -22391,8 +22508,12 @@
       <c r="H82" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I82" s="17"/>
-      <c r="J82" s="77"/>
+      <c r="I82" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="77" t="s">
+        <v>260</v>
+      </c>
       <c r="K82" s="43"/>
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
@@ -22644,15 +22765,15 @@
       <c r="A83" s="6">
         <v>17</v>
       </c>
-      <c r="B83" s="84" t="s">
+      <c r="B83" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C83" s="88" t="s">
+      <c r="C83" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D83" s="84"/>
-      <c r="E83" s="89" t="s">
-        <v>186</v>
+      <c r="D83" s="81"/>
+      <c r="E83" s="85" t="s">
+        <v>185</v>
       </c>
       <c r="F83" s="46"/>
       <c r="G83" s="41" t="s">
@@ -22914,15 +23035,15 @@
       <c r="A84" s="6">
         <v>18</v>
       </c>
-      <c r="B84" s="84" t="s">
+      <c r="B84" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C84" s="88" t="s">
+      <c r="C84" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D84" s="84"/>
-      <c r="E84" s="89" t="s">
-        <v>187</v>
+      <c r="D84" s="81"/>
+      <c r="E84" s="85" t="s">
+        <v>186</v>
       </c>
       <c r="F84" s="46"/>
       <c r="G84" s="41" t="s">
@@ -23184,15 +23305,15 @@
       <c r="A85" s="6">
         <v>19</v>
       </c>
-      <c r="B85" s="84" t="s">
+      <c r="B85" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C85" s="88" t="s">
+      <c r="C85" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D85" s="84"/>
-      <c r="E85" s="89" t="s">
-        <v>188</v>
+      <c r="D85" s="81"/>
+      <c r="E85" s="85" t="s">
+        <v>187</v>
       </c>
       <c r="F85" s="46"/>
       <c r="G85" s="41" t="s">
@@ -23450,19 +23571,19 @@
       <c r="IU85" s="40"/>
       <c r="IV85" s="40"/>
     </row>
-    <row r="86" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>20</v>
       </c>
-      <c r="B86" s="84" t="s">
+      <c r="B86" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C86" s="88" t="s">
+      <c r="C86" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D86" s="84"/>
-      <c r="E86" s="89" t="s">
-        <v>189</v>
+      <c r="D86" s="81"/>
+      <c r="E86" s="85" t="s">
+        <v>188</v>
       </c>
       <c r="F86" s="46"/>
       <c r="G86" s="41" t="s">
@@ -23471,8 +23592,12 @@
       <c r="H86" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I86" s="17"/>
-      <c r="J86" s="77"/>
+      <c r="I86" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="77" t="s">
+        <v>261</v>
+      </c>
       <c r="K86" s="43"/>
       <c r="L86" s="16"/>
       <c r="M86" s="16"/>
@@ -23724,15 +23849,15 @@
       <c r="A87" s="6">
         <v>21</v>
       </c>
-      <c r="B87" s="84" t="s">
+      <c r="B87" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C87" s="88" t="s">
+      <c r="C87" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D87" s="84"/>
-      <c r="E87" s="89" t="s">
-        <v>190</v>
+      <c r="D87" s="81"/>
+      <c r="E87" s="85" t="s">
+        <v>189</v>
       </c>
       <c r="F87" s="46"/>
       <c r="G87" s="41" t="s">
@@ -23994,15 +24119,15 @@
       <c r="A88" s="6">
         <v>22</v>
       </c>
-      <c r="B88" s="84" t="s">
+      <c r="B88" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C88" s="88" t="s">
+      <c r="C88" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D88" s="84"/>
-      <c r="E88" s="89" t="s">
-        <v>191</v>
+      <c r="D88" s="81"/>
+      <c r="E88" s="85" t="s">
+        <v>190</v>
       </c>
       <c r="F88" s="46"/>
       <c r="G88" s="41" t="s">
@@ -24260,19 +24385,19 @@
       <c r="IU88" s="40"/>
       <c r="IV88" s="40"/>
     </row>
-    <row r="89" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:256" s="37" customFormat="1" ht="342" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>23</v>
       </c>
-      <c r="B89" s="84" t="s">
+      <c r="B89" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C89" s="88" t="s">
+      <c r="C89" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D89" s="84"/>
-      <c r="E89" s="89" t="s">
-        <v>192</v>
+      <c r="D89" s="81"/>
+      <c r="E89" s="85" t="s">
+        <v>191</v>
       </c>
       <c r="F89" s="46"/>
       <c r="G89" s="41" t="s">
@@ -24281,8 +24406,12 @@
       <c r="H89" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I89" s="17"/>
-      <c r="J89" s="77"/>
+      <c r="I89" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="77" t="s">
+        <v>266</v>
+      </c>
       <c r="K89" s="43"/>
       <c r="L89" s="16"/>
       <c r="M89" s="16"/>
@@ -24534,15 +24663,15 @@
       <c r="A90" s="6">
         <v>24</v>
       </c>
-      <c r="B90" s="84" t="s">
+      <c r="B90" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C90" s="88" t="s">
+      <c r="C90" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D90" s="84"/>
-      <c r="E90" s="89" t="s">
-        <v>194</v>
+      <c r="D90" s="81"/>
+      <c r="E90" s="85" t="s">
+        <v>193</v>
       </c>
       <c r="F90" s="46"/>
       <c r="G90" s="41" t="s">
@@ -24800,19 +24929,19 @@
       <c r="IU90" s="40"/>
       <c r="IV90" s="40"/>
     </row>
-    <row r="91" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>25</v>
       </c>
-      <c r="B91" s="84" t="s">
+      <c r="B91" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C91" s="88" t="s">
+      <c r="C91" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="D91" s="84"/>
-      <c r="E91" s="89" t="s">
-        <v>193</v>
+      <c r="D91" s="81"/>
+      <c r="E91" s="85" t="s">
+        <v>192</v>
       </c>
       <c r="F91" s="46"/>
       <c r="G91" s="41" t="s">
@@ -24821,8 +24950,12 @@
       <c r="H91" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I91" s="17"/>
-      <c r="J91" s="77"/>
+      <c r="I91" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="77" t="s">
+        <v>271</v>
+      </c>
       <c r="K91" s="43"/>
       <c r="L91" s="16"/>
       <c r="M91" s="16"/>
@@ -25074,15 +25207,15 @@
       <c r="A92" s="6">
         <v>26</v>
       </c>
-      <c r="B92" s="84" t="s">
+      <c r="B92" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="C92" s="88" t="s">
+      <c r="C92" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="D92" s="84"/>
-      <c r="E92" s="89" t="s">
-        <v>196</v>
+      <c r="D92" s="81"/>
+      <c r="E92" s="85" t="s">
+        <v>195</v>
       </c>
       <c r="F92" s="46"/>
       <c r="G92" s="41" t="s">
@@ -25091,7 +25224,9 @@
       <c r="H92" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I92" s="17"/>
+      <c r="I92" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J92" s="77"/>
       <c r="K92" s="43"/>
       <c r="L92" s="16"/>
@@ -25340,19 +25475,19 @@
       <c r="IU92" s="40"/>
       <c r="IV92" s="40"/>
     </row>
-    <row r="93" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>27</v>
       </c>
-      <c r="B93" s="84" t="s">
+      <c r="B93" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C93" s="88" t="s">
+      <c r="C93" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D93" s="84"/>
-      <c r="E93" s="89" t="s">
-        <v>199</v>
+      <c r="D93" s="81"/>
+      <c r="E93" s="85" t="s">
+        <v>198</v>
       </c>
       <c r="F93" s="46"/>
       <c r="G93" s="41" t="s">
@@ -25361,7 +25496,9 @@
       <c r="H93" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I93" s="17"/>
+      <c r="I93" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J93" s="77"/>
       <c r="K93" s="43"/>
       <c r="L93" s="16"/>
@@ -25610,19 +25747,19 @@
       <c r="IU93" s="40"/>
       <c r="IV93" s="40"/>
     </row>
-    <row r="94" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>28</v>
       </c>
-      <c r="B94" s="84" t="s">
+      <c r="B94" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C94" s="88" t="s">
+      <c r="C94" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D94" s="84"/>
-      <c r="E94" s="89" t="s">
-        <v>200</v>
+      <c r="D94" s="81"/>
+      <c r="E94" s="85" t="s">
+        <v>199</v>
       </c>
       <c r="F94" s="46"/>
       <c r="G94" s="41" t="s">
@@ -25631,8 +25768,12 @@
       <c r="H94" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I94" s="17"/>
-      <c r="J94" s="77"/>
+      <c r="I94" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J94" s="104" t="s">
+        <v>277</v>
+      </c>
       <c r="K94" s="43"/>
       <c r="L94" s="16"/>
       <c r="M94" s="16"/>
@@ -25880,19 +26021,19 @@
       <c r="IU94" s="40"/>
       <c r="IV94" s="40"/>
     </row>
-    <row r="95" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>29</v>
       </c>
-      <c r="B95" s="84" t="s">
+      <c r="B95" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C95" s="88" t="s">
+      <c r="C95" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D95" s="84"/>
-      <c r="E95" s="89" t="s">
-        <v>201</v>
+      <c r="D95" s="81"/>
+      <c r="E95" s="85" t="s">
+        <v>200</v>
       </c>
       <c r="F95" s="46"/>
       <c r="G95" s="41" t="s">
@@ -25901,8 +26042,10 @@
       <c r="H95" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I95" s="17"/>
-      <c r="J95" s="77"/>
+      <c r="I95" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J95" s="124"/>
       <c r="K95" s="43"/>
       <c r="L95" s="16"/>
       <c r="M95" s="16"/>
@@ -26150,19 +26293,19 @@
       <c r="IU95" s="40"/>
       <c r="IV95" s="40"/>
     </row>
-    <row r="96" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>30</v>
       </c>
-      <c r="B96" s="84" t="s">
+      <c r="B96" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C96" s="88" t="s">
+      <c r="C96" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D96" s="84"/>
-      <c r="E96" s="89" t="s">
-        <v>202</v>
+      <c r="D96" s="81"/>
+      <c r="E96" s="85" t="s">
+        <v>201</v>
       </c>
       <c r="F96" s="46"/>
       <c r="G96" s="41" t="s">
@@ -26171,8 +26314,10 @@
       <c r="H96" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I96" s="17"/>
-      <c r="J96" s="77"/>
+      <c r="I96" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" s="124"/>
       <c r="K96" s="43"/>
       <c r="L96" s="16"/>
       <c r="M96" s="16"/>
@@ -26420,19 +26565,19 @@
       <c r="IU96" s="40"/>
       <c r="IV96" s="40"/>
     </row>
-    <row r="97" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:256" s="37" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>31</v>
       </c>
-      <c r="B97" s="84" t="s">
+      <c r="B97" s="81" t="s">
         <v>139</v>
       </c>
-      <c r="C97" s="88" t="s">
+      <c r="C97" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D97" s="84"/>
-      <c r="E97" s="89" t="s">
-        <v>203</v>
+      <c r="D97" s="81"/>
+      <c r="E97" s="85" t="s">
+        <v>202</v>
       </c>
       <c r="F97" s="46"/>
       <c r="G97" s="41" t="s">
@@ -26441,8 +26586,10 @@
       <c r="H97" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I97" s="17"/>
-      <c r="J97" s="77"/>
+      <c r="I97" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="105"/>
       <c r="K97" s="43"/>
       <c r="L97" s="16"/>
       <c r="M97" s="16"/>
@@ -26694,15 +26841,15 @@
       <c r="A98" s="6">
         <v>32</v>
       </c>
-      <c r="B98" s="84" t="s">
+      <c r="B98" s="81" t="s">
+        <v>204</v>
+      </c>
+      <c r="C98" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="81"/>
+      <c r="E98" s="85" t="s">
         <v>205</v>
-      </c>
-      <c r="C98" s="88" t="s">
-        <v>204</v>
-      </c>
-      <c r="D98" s="84"/>
-      <c r="E98" s="89" t="s">
-        <v>206</v>
       </c>
       <c r="F98" s="46"/>
       <c r="G98" s="41" t="s">
@@ -26964,15 +27111,15 @@
       <c r="A99" s="6">
         <v>33</v>
       </c>
-      <c r="B99" s="84" t="s">
-        <v>205</v>
-      </c>
-      <c r="C99" s="88" t="s">
+      <c r="B99" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="D99" s="84"/>
-      <c r="E99" s="89" t="s">
-        <v>207</v>
+      <c r="C99" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D99" s="81"/>
+      <c r="E99" s="85" t="s">
+        <v>206</v>
       </c>
       <c r="F99" s="46"/>
       <c r="G99" s="41" t="s">
@@ -27230,19 +27377,19 @@
       <c r="IU99" s="40"/>
       <c r="IV99" s="40"/>
     </row>
-    <row r="100" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>34</v>
       </c>
-      <c r="B100" s="84" t="s">
-        <v>205</v>
-      </c>
-      <c r="C100" s="88" t="s">
+      <c r="B100" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="D100" s="84"/>
-      <c r="E100" s="89" t="s">
-        <v>208</v>
+      <c r="C100" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D100" s="81"/>
+      <c r="E100" s="85" t="s">
+        <v>207</v>
       </c>
       <c r="F100" s="46"/>
       <c r="G100" s="41" t="s">
@@ -27251,8 +27398,12 @@
       <c r="H100" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I100" s="17"/>
-      <c r="J100" s="77"/>
+      <c r="I100" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="77" t="s">
+        <v>276</v>
+      </c>
       <c r="K100" s="43"/>
       <c r="L100" s="16"/>
       <c r="M100" s="16"/>
@@ -27500,19 +27651,19 @@
       <c r="IU100" s="40"/>
       <c r="IV100" s="40"/>
     </row>
-    <row r="101" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>35</v>
       </c>
-      <c r="B101" s="84" t="s">
+      <c r="B101" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C101" s="88" t="s">
+      <c r="C101" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D101" s="84"/>
-      <c r="E101" s="89" t="s">
-        <v>219</v>
+      <c r="D101" s="81"/>
+      <c r="E101" s="85" t="s">
+        <v>218</v>
       </c>
       <c r="F101" s="46"/>
       <c r="G101" s="41" t="s">
@@ -27521,7 +27672,9 @@
       <c r="H101" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I101" s="17"/>
+      <c r="I101" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J101" s="77"/>
       <c r="K101" s="43"/>
       <c r="L101" s="16"/>
@@ -27770,19 +27923,19 @@
       <c r="IU101" s="40"/>
       <c r="IV101" s="40"/>
     </row>
-    <row r="102" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>36</v>
       </c>
-      <c r="B102" s="84" t="s">
+      <c r="B102" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C102" s="88" t="s">
+      <c r="C102" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D102" s="84"/>
-      <c r="E102" s="89" t="s">
-        <v>199</v>
+      <c r="D102" s="81"/>
+      <c r="E102" s="85" t="s">
+        <v>198</v>
       </c>
       <c r="F102" s="46"/>
       <c r="G102" s="41" t="s">
@@ -27791,7 +27944,9 @@
       <c r="H102" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I102" s="17"/>
+      <c r="I102" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J102" s="77"/>
       <c r="K102" s="43"/>
       <c r="L102" s="16"/>
@@ -28040,15 +28195,15 @@
       <c r="IU102" s="40"/>
       <c r="IV102" s="40"/>
     </row>
-    <row r="103" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:256" s="37" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
-      <c r="B103" s="84"/>
-      <c r="C103" s="88" t="s">
+      <c r="B103" s="81"/>
+      <c r="C103" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D103" s="84"/>
-      <c r="E103" s="89" t="s">
-        <v>212</v>
+      <c r="D103" s="81"/>
+      <c r="E103" s="85" t="s">
+        <v>211</v>
       </c>
       <c r="F103" s="46"/>
       <c r="G103" s="41" t="s">
@@ -28310,15 +28465,15 @@
       <c r="A104" s="6">
         <v>37</v>
       </c>
-      <c r="B104" s="84" t="s">
+      <c r="B104" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C104" s="88" t="s">
+      <c r="C104" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D104" s="84"/>
-      <c r="E104" s="89" t="s">
-        <v>213</v>
+      <c r="D104" s="81"/>
+      <c r="E104" s="85" t="s">
+        <v>212</v>
       </c>
       <c r="F104" s="46"/>
       <c r="G104" s="41" t="s">
@@ -28327,7 +28482,9 @@
       <c r="H104" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I104" s="17"/>
+      <c r="I104" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J104" s="77"/>
       <c r="K104" s="43"/>
       <c r="L104" s="16"/>
@@ -28580,15 +28737,15 @@
       <c r="A105" s="6">
         <v>38</v>
       </c>
-      <c r="B105" s="84" t="s">
+      <c r="B105" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C105" s="88" t="s">
+      <c r="C105" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D105" s="84"/>
-      <c r="E105" s="89" t="s">
-        <v>214</v>
+      <c r="D105" s="81"/>
+      <c r="E105" s="85" t="s">
+        <v>213</v>
       </c>
       <c r="F105" s="46"/>
       <c r="G105" s="41" t="s">
@@ -28597,7 +28754,9 @@
       <c r="H105" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I105" s="17"/>
+      <c r="I105" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J105" s="77"/>
       <c r="K105" s="43"/>
       <c r="L105" s="16"/>
@@ -28850,15 +29009,15 @@
       <c r="A106" s="6">
         <v>39</v>
       </c>
-      <c r="B106" s="84" t="s">
+      <c r="B106" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C106" s="88" t="s">
+      <c r="C106" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D106" s="84"/>
-      <c r="E106" s="89" t="s">
-        <v>215</v>
+      <c r="D106" s="81"/>
+      <c r="E106" s="85" t="s">
+        <v>214</v>
       </c>
       <c r="F106" s="46"/>
       <c r="G106" s="41" t="s">
@@ -28867,7 +29026,9 @@
       <c r="H106" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I106" s="17"/>
+      <c r="I106" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J106" s="77"/>
       <c r="K106" s="43"/>
       <c r="L106" s="16"/>
@@ -29120,15 +29281,15 @@
       <c r="A107" s="6">
         <v>40</v>
       </c>
-      <c r="B107" s="84" t="s">
+      <c r="B107" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C107" s="88" t="s">
+      <c r="C107" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D107" s="84"/>
-      <c r="E107" s="89" t="s">
-        <v>216</v>
+      <c r="D107" s="81"/>
+      <c r="E107" s="85" t="s">
+        <v>215</v>
       </c>
       <c r="F107" s="46"/>
       <c r="G107" s="41" t="s">
@@ -29137,7 +29298,9 @@
       <c r="H107" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I107" s="17"/>
+      <c r="I107" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J107" s="77"/>
       <c r="K107" s="43"/>
       <c r="L107" s="16"/>
@@ -29386,19 +29549,19 @@
       <c r="IU107" s="40"/>
       <c r="IV107" s="40"/>
     </row>
-    <row r="108" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41</v>
       </c>
-      <c r="B108" s="84" t="s">
+      <c r="B108" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C108" s="88" t="s">
+      <c r="C108" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D108" s="84"/>
-      <c r="E108" s="89" t="s">
-        <v>218</v>
+      <c r="D108" s="81"/>
+      <c r="E108" s="85" t="s">
+        <v>217</v>
       </c>
       <c r="F108" s="46"/>
       <c r="G108" s="41" t="s">
@@ -29407,7 +29570,9 @@
       <c r="H108" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I108" s="17"/>
+      <c r="I108" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J108" s="77"/>
       <c r="K108" s="43"/>
       <c r="L108" s="16"/>
@@ -29656,19 +29821,19 @@
       <c r="IU108" s="40"/>
       <c r="IV108" s="40"/>
     </row>
-    <row r="109" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>42</v>
       </c>
-      <c r="B109" s="84" t="s">
+      <c r="B109" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="C109" s="88" t="s">
+      <c r="C109" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D109" s="84"/>
-      <c r="E109" s="89" t="s">
-        <v>217</v>
+      <c r="D109" s="81"/>
+      <c r="E109" s="85" t="s">
+        <v>216</v>
       </c>
       <c r="F109" s="46"/>
       <c r="G109" s="41" t="s">
@@ -29677,7 +29842,9 @@
       <c r="H109" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I109" s="17"/>
+      <c r="I109" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J109" s="77"/>
       <c r="K109" s="43"/>
       <c r="L109" s="16"/>
@@ -29930,15 +30097,15 @@
       <c r="A110" s="6">
         <v>43</v>
       </c>
-      <c r="B110" s="84" t="s">
+      <c r="B110" s="81" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="D110" s="81"/>
+      <c r="E110" s="85" t="s">
         <v>210</v>
-      </c>
-      <c r="C110" s="88" t="s">
-        <v>209</v>
-      </c>
-      <c r="D110" s="84"/>
-      <c r="E110" s="89" t="s">
-        <v>211</v>
       </c>
       <c r="F110" s="46"/>
       <c r="G110" s="41" t="s">
@@ -30200,15 +30367,15 @@
       <c r="A111" s="6">
         <v>44</v>
       </c>
-      <c r="B111" s="84" t="s">
+      <c r="B111" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="C111" s="88" t="s">
+      <c r="C111" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="D111" s="84"/>
-      <c r="E111" s="89" t="s">
-        <v>220</v>
+      <c r="D111" s="81"/>
+      <c r="E111" s="85" t="s">
+        <v>219</v>
       </c>
       <c r="F111" s="46"/>
       <c r="G111" s="41" t="s">
@@ -30470,15 +30637,15 @@
       <c r="A112" s="6">
         <v>45</v>
       </c>
-      <c r="B112" s="84" t="s">
+      <c r="B112" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="C112" s="88" t="s">
+      <c r="C112" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="D112" s="84"/>
-      <c r="E112" s="89" t="s">
-        <v>222</v>
+      <c r="D112" s="81"/>
+      <c r="E112" s="85" t="s">
+        <v>221</v>
       </c>
       <c r="F112" s="46"/>
       <c r="G112" s="41" t="s">
@@ -30740,15 +30907,15 @@
       <c r="A113" s="6">
         <v>46</v>
       </c>
-      <c r="B113" s="84" t="s">
+      <c r="B113" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="C113" s="88" t="s">
+      <c r="C113" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="84"/>
-      <c r="E113" s="89" t="s">
-        <v>221</v>
+      <c r="D113" s="81"/>
+      <c r="E113" s="85" t="s">
+        <v>220</v>
       </c>
       <c r="F113" s="46"/>
       <c r="G113" s="41" t="s">
@@ -31010,18 +31177,18 @@
       <c r="A114" s="6">
         <v>47</v>
       </c>
-      <c r="B114" s="84" t="s">
+      <c r="B114" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="C114" s="88" t="s">
+      <c r="C114" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="D114" s="84"/>
-      <c r="E114" s="89" t="s">
+      <c r="D114" s="81"/>
+      <c r="E114" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="F114" s="46" t="s">
         <v>224</v>
-      </c>
-      <c r="F114" s="46" t="s">
-        <v>225</v>
       </c>
       <c r="G114" s="41" t="s">
         <v>51</v>
@@ -31278,21 +31445,21 @@
       <c r="IU114" s="40"/>
       <c r="IV114" s="40"/>
     </row>
-    <row r="115" spans="1:256" s="37" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:256" s="37" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>48</v>
       </c>
-      <c r="B115" s="84" t="s">
+      <c r="B115" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="C115" s="88" t="s">
+      <c r="C115" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="D115" s="84" t="s">
+      <c r="D115" s="81" t="s">
+        <v>225</v>
+      </c>
+      <c r="E115" s="85" t="s">
         <v>226</v>
-      </c>
-      <c r="E115" s="89" t="s">
-        <v>227</v>
       </c>
       <c r="F115" s="46"/>
       <c r="G115" s="41" t="s">
@@ -31554,15 +31721,15 @@
       <c r="A116" s="6">
         <v>49</v>
       </c>
-      <c r="B116" s="84" t="s">
-        <v>223</v>
-      </c>
-      <c r="C116" s="88" t="s">
+      <c r="B116" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="C116" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D116" s="84"/>
-      <c r="E116" s="89" t="s">
-        <v>178</v>
+      <c r="D116" s="81"/>
+      <c r="E116" s="85" t="s">
+        <v>177</v>
       </c>
       <c r="F116" s="46"/>
       <c r="G116" s="41" t="s">
@@ -31824,15 +31991,15 @@
       <c r="A117" s="6">
         <v>50</v>
       </c>
-      <c r="B117" s="84" t="s">
-        <v>223</v>
-      </c>
-      <c r="C117" s="88" t="s">
+      <c r="B117" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="C117" s="84" t="s">
         <v>96</v>
       </c>
-      <c r="D117" s="84"/>
-      <c r="E117" s="89" t="s">
-        <v>198</v>
+      <c r="D117" s="81"/>
+      <c r="E117" s="85" t="s">
+        <v>197</v>
       </c>
       <c r="F117" s="46"/>
       <c r="G117" s="41" t="s">
@@ -32090,24 +32257,26 @@
       <c r="IU117" s="40"/>
       <c r="IV117" s="40"/>
     </row>
-    <row r="118" spans="1:256" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:256" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>51</v>
       </c>
-      <c r="B118" s="84" t="s">
+      <c r="B118" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="C118" s="88" t="s">
+      <c r="C118" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="D118" s="84"/>
-      <c r="E118" s="89" t="s">
-        <v>228</v>
+      <c r="D118" s="81"/>
+      <c r="E118" s="85" t="s">
+        <v>227</v>
       </c>
       <c r="F118" s="46"/>
       <c r="G118" s="41"/>
       <c r="H118" s="42"/>
-      <c r="I118" s="17"/>
+      <c r="I118" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="J118" s="77"/>
       <c r="K118" s="43"/>
       <c r="L118" s="16"/>
@@ -32360,27 +32529,31 @@
       <c r="A119" s="6">
         <v>52</v>
       </c>
-      <c r="B119" s="84" t="s">
+      <c r="B119" s="81" t="s">
+        <v>228</v>
+      </c>
+      <c r="C119" s="91" t="s">
         <v>229</v>
       </c>
-      <c r="C119" s="81" t="s">
+      <c r="D119" s="78" t="s">
         <v>230</v>
       </c>
-      <c r="D119" s="79" t="s">
+      <c r="E119" s="86" t="s">
         <v>231</v>
       </c>
-      <c r="E119" s="90" t="s">
-        <v>232</v>
-      </c>
       <c r="F119" s="46"/>
-      <c r="G119" s="81" t="s">
+      <c r="G119" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="H119" s="83" t="s">
         <v>246</v>
       </c>
-      <c r="H119" s="87" t="s">
-        <v>247</v>
-      </c>
-      <c r="I119" s="17"/>
-      <c r="J119" s="77"/>
+      <c r="I119" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="77" t="s">
+        <v>262</v>
+      </c>
       <c r="K119" s="43"/>
       <c r="L119" s="16"/>
       <c r="M119" s="16"/>
@@ -32632,27 +32805,31 @@
       <c r="A120" s="6">
         <v>53</v>
       </c>
-      <c r="B120" s="84" t="s">
+      <c r="B120" s="81" t="s">
+        <v>228</v>
+      </c>
+      <c r="C120" s="92" t="s">
         <v>229</v>
       </c>
-      <c r="C120" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="D120" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="E120" s="90" t="s">
-        <v>250</v>
+      <c r="D120" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="E120" s="86" t="s">
+        <v>249</v>
       </c>
       <c r="F120" s="46"/>
-      <c r="G120" s="81" t="s">
+      <c r="G120" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="H120" s="83" t="s">
         <v>246</v>
       </c>
-      <c r="H120" s="87" t="s">
-        <v>247</v>
-      </c>
-      <c r="I120" s="17"/>
-      <c r="J120" s="77"/>
+      <c r="I120" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="77" t="s">
+        <v>262</v>
+      </c>
       <c r="K120" s="43"/>
       <c r="L120" s="16"/>
       <c r="M120" s="16"/>
@@ -32904,24 +33081,24 @@
       <c r="A121" s="6">
         <v>54</v>
       </c>
-      <c r="B121" s="91" t="s">
-        <v>234</v>
-      </c>
-      <c r="C121" s="81" t="s">
+      <c r="B121" s="87" t="s">
+        <v>233</v>
+      </c>
+      <c r="C121" s="91" t="s">
         <v>143</v>
       </c>
-      <c r="D121" s="80" t="s">
+      <c r="D121" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="E121" s="90" t="s">
-        <v>251</v>
+      <c r="E121" s="86" t="s">
+        <v>250</v>
       </c>
       <c r="F121" s="46"/>
-      <c r="G121" s="81" t="s">
+      <c r="G121" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="H121" s="83" t="s">
         <v>246</v>
-      </c>
-      <c r="H121" s="87" t="s">
-        <v>247</v>
       </c>
       <c r="I121" s="17"/>
       <c r="J121" s="77"/>
@@ -33176,24 +33353,24 @@
       <c r="A122" s="6">
         <v>55</v>
       </c>
-      <c r="B122" s="84" t="s">
+      <c r="B122" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="C122" s="81" t="s">
+      <c r="C122" s="125" t="s">
+        <v>234</v>
+      </c>
+      <c r="D122" s="78" t="s">
         <v>235</v>
       </c>
-      <c r="D122" s="79" t="s">
+      <c r="E122" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="E122" s="90" t="s">
-        <v>237</v>
-      </c>
       <c r="F122" s="46"/>
-      <c r="G122" s="81" t="s">
+      <c r="G122" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="H122" s="83" t="s">
         <v>246</v>
-      </c>
-      <c r="H122" s="87" t="s">
-        <v>247</v>
       </c>
       <c r="I122" s="17"/>
       <c r="J122" s="77"/>
@@ -33448,22 +33625,22 @@
       <c r="A123" s="6">
         <v>56</v>
       </c>
-      <c r="B123" s="84" t="s">
+      <c r="B123" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C123" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="C123" s="82" t="s">
-        <v>239</v>
-      </c>
-      <c r="D123" s="79"/>
-      <c r="E123" s="90" t="s">
-        <v>252</v>
+      <c r="D123" s="78"/>
+      <c r="E123" s="86" t="s">
+        <v>251</v>
       </c>
       <c r="F123" s="46"/>
-      <c r="G123" s="81" t="s">
+      <c r="G123" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="H123" s="83" t="s">
         <v>246</v>
-      </c>
-      <c r="H123" s="87" t="s">
-        <v>247</v>
       </c>
       <c r="I123" s="17"/>
       <c r="J123" s="77"/>
@@ -33714,29 +33891,33 @@
       <c r="IU123" s="40"/>
       <c r="IV123" s="40"/>
     </row>
-    <row r="124" spans="1:256" s="37" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:256" s="37" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>57</v>
       </c>
-      <c r="B124" s="84" t="s">
-        <v>238</v>
-      </c>
-      <c r="C124" s="83" t="s">
+      <c r="B124" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C124" s="94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D124" s="81"/>
+      <c r="E124" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="D124" s="84"/>
-      <c r="E124" s="85" t="s">
-        <v>241</v>
-      </c>
       <c r="F124" s="46"/>
-      <c r="G124" s="81" t="s">
+      <c r="G124" s="80" t="s">
+        <v>247</v>
+      </c>
+      <c r="H124" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="H124" s="87" t="s">
-        <v>249</v>
-      </c>
-      <c r="I124" s="17"/>
-      <c r="J124" s="77"/>
+      <c r="I124" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="104" t="s">
+        <v>274</v>
+      </c>
       <c r="K124" s="43"/>
       <c r="L124" s="16"/>
       <c r="M124" s="16"/>
@@ -33984,29 +34165,31 @@
       <c r="IU124" s="40"/>
       <c r="IV124" s="40"/>
     </row>
-    <row r="125" spans="1:256" s="37" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:256" s="37" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>58</v>
       </c>
-      <c r="B125" s="84" t="s">
-        <v>238</v>
-      </c>
-      <c r="C125" s="86" t="s">
+      <c r="B125" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C125" s="95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" s="81"/>
+      <c r="E125" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="D125" s="84"/>
-      <c r="E125" s="85" t="s">
-        <v>243</v>
-      </c>
       <c r="F125" s="46"/>
-      <c r="G125" s="81" t="s">
+      <c r="G125" s="80" t="s">
+        <v>247</v>
+      </c>
+      <c r="H125" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="H125" s="87" t="s">
-        <v>249</v>
-      </c>
-      <c r="I125" s="17"/>
-      <c r="J125" s="77"/>
+      <c r="I125" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="124"/>
       <c r="K125" s="43"/>
       <c r="L125" s="16"/>
       <c r="M125" s="16"/>
@@ -34254,29 +34437,31 @@
       <c r="IU125" s="40"/>
       <c r="IV125" s="40"/>
     </row>
-    <row r="126" spans="1:256" s="37" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:256" s="37" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>59</v>
       </c>
-      <c r="B126" s="84" t="s">
-        <v>238</v>
-      </c>
-      <c r="C126" s="86" t="s">
+      <c r="B126" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C126" s="95" t="s">
+        <v>243</v>
+      </c>
+      <c r="D126" s="81"/>
+      <c r="E126" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="D126" s="84"/>
-      <c r="E126" s="85" t="s">
-        <v>245</v>
-      </c>
       <c r="F126" s="46"/>
-      <c r="G126" s="81" t="s">
+      <c r="G126" s="80" t="s">
+        <v>247</v>
+      </c>
+      <c r="H126" s="83" t="s">
         <v>248</v>
       </c>
-      <c r="H126" s="87" t="s">
-        <v>249</v>
-      </c>
-      <c r="I126" s="17"/>
-      <c r="J126" s="77"/>
+      <c r="I126" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="105"/>
       <c r="K126" s="43"/>
       <c r="L126" s="16"/>
       <c r="M126" s="16"/>
@@ -34823,10 +35008,10 @@
       <c r="J129" s="10"/>
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
-      <c r="M129" s="95" t="s">
+      <c r="M129" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="N129" s="95"/>
+      <c r="N129" s="100"/>
       <c r="O129" s="10"/>
       <c r="P129" s="11"/>
       <c r="Q129" s="11"/>
@@ -37968,47 +38153,25 @@
       <c r="E146" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="A11:IV118"/>
+  <autoFilter ref="A11:IV118" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
-      <selection activeCell="F21" sqref="F21"/>
+    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
+      <selection activeCell="C63" sqref="C63:D63"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-      <autoFilter ref="B9:Y31"/>
+      <autoFilter ref="B9:Y51" xr:uid="{0A313221-9F3C-4991-A8FF-CEFFF16A13E6}"/>
     </customSheetView>
-    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
-      <selection activeCell="K20" sqref="K20"/>
+    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
+      <selection activeCell="K12" sqref="K12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="B9:Y31"/>
-    </customSheetView>
-    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
-      <selection activeCell="K23" sqref="K23"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId3"/>
-      <autoFilter ref="B9:Y31"/>
-    </customSheetView>
-    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
-      <selection activeCell="C238" sqref="C238:D238"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="B10:Z230">
-        <filterColumn colId="7">
-          <filters>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
-            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
+      <autoFilter ref="B9:Y31" xr:uid="{D9846EB7-C3B8-4D5D-94B5-E23052C482CA}"/>
     </customSheetView>
     <customSheetView guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" topLeftCell="K144">
       <selection activeCell="O76" sqref="O76"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="B10:Z230">
+      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+      <autoFilter ref="B10:Z230" xr:uid="{A66FC9BF-834D-409F-BA3B-5D09237239B3}">
         <filterColumn colId="7">
           <filters>
             <filter val="ИГН, ГТЭП"/>
@@ -38024,29 +38187,50 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
-      <selection activeCell="K12" sqref="K12"/>
+    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
+      <selection activeCell="C238" sqref="C238:D238"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
+      <autoFilter ref="B10:Z230" xr:uid="{D4480B49-2403-407E-8830-E0B9C9B6290D}">
+        <filterColumn colId="7">
+          <filters>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
+            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
+    </customSheetView>
+    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
+      <selection activeCell="K23" sqref="K23"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId5"/>
+      <autoFilter ref="B9:Y31" xr:uid="{B79DD8C0-CB0D-4518-B303-C8E6FEA9F2F7}"/>
+    </customSheetView>
+    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
+      <selection activeCell="K20" sqref="K20"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="B9:Y31"/>
+      <autoFilter ref="B9:Y31" xr:uid="{42420926-DB20-404C-8E48-9D76B39FBB6B}"/>
     </customSheetView>
-    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
-      <selection activeCell="C63" sqref="C63:D63"/>
+    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
+      <selection activeCell="F21" sqref="F21"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId7"/>
-      <autoFilter ref="B9:Y51"/>
+      <autoFilter ref="B9:Y31" xr:uid="{43BD1EE2-F512-44F0-85C0-393B2FFF573B}"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="31">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
+  <mergeCells count="33">
+    <mergeCell ref="J124:J126"/>
+    <mergeCell ref="J94:J97"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="M129:N129"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="A8:A9"/>
@@ -38063,22 +38247,25 @@
     <mergeCell ref="I38:K38"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127 I39:I65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I12:I37 I67:I127 I39:I65" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$B$131:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:N37 N67:N127 N39:N65" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$B$135:$B$136</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12:L37 L67:L127 L39:L65" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$B$138:$B$140</formula1>
     </dataValidation>
   </dataValidations>
@@ -38094,7 +38281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -38155,11 +38342,11 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -38182,12 +38369,12 @@
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -38209,11 +38396,11 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="48"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -38236,12 +38423,12 @@
       <c r="W4" s="3"/>
     </row>
     <row r="5" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -38315,39 +38502,39 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:255" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="99" t="s">
+      <c r="D8" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="99" t="s">
+      <c r="F8" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="116" t="s">
+      <c r="G8" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="117"/>
-      <c r="K8" s="99" t="s">
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="99"/>
-      <c r="M8" s="102" t="s">
+      <c r="L8" s="97"/>
+      <c r="M8" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="102"/>
-      <c r="O8" s="96" t="s">
+      <c r="N8" s="98"/>
+      <c r="O8" s="101" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="34" t="s">
@@ -38372,22 +38559,22 @@
       </c>
     </row>
     <row r="9" spans="1:255" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="120"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
       <c r="G9" s="25" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="116" t="s">
+      <c r="I9" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="117"/>
+      <c r="J9" s="115"/>
       <c r="K9" s="19" t="s">
         <v>8</v>
       </c>
@@ -38400,7 +38587,7 @@
       <c r="N9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="97"/>
+      <c r="O9" s="102"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35" t="s">
         <v>6</v>
@@ -38421,28 +38608,28 @@
       </c>
     </row>
     <row r="10" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="105" t="s">
+      <c r="B10" s="106"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="94" t="s">
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="94"/>
-      <c r="M10" s="93" t="s">
+      <c r="L10" s="106"/>
+      <c r="M10" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="93"/>
+      <c r="N10" s="107"/>
       <c r="O10" s="47" t="s">
         <v>17</v>
       </c>
@@ -38466,8 +38653,8 @@
       <c r="F11" s="59"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="118"/>
       <c r="K11" s="6"/>
       <c r="L11" s="16"/>
       <c r="M11" s="71"/>
@@ -38725,8 +38912,8 @@
       <c r="F12" s="59"/>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="118"/>
       <c r="K12" s="6"/>
       <c r="L12" s="16"/>
       <c r="M12" s="71"/>
@@ -38984,8 +39171,8 @@
       <c r="F13" s="59"/>
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="118"/>
       <c r="K13" s="6"/>
       <c r="L13" s="16"/>
       <c r="M13" s="71"/>
@@ -39243,8 +39430,8 @@
       <c r="F14" s="59"/>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="109"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="118"/>
       <c r="K14" s="6"/>
       <c r="L14" s="16"/>
       <c r="M14" s="71"/>
@@ -39502,8 +39689,8 @@
       <c r="F15" s="59"/>
       <c r="G15" s="70"/>
       <c r="H15" s="70"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="109"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="118"/>
       <c r="K15" s="6"/>
       <c r="L15" s="16"/>
       <c r="M15" s="71"/>
@@ -39751,28 +39938,28 @@
       <c r="IU15" s="40"/>
     </row>
     <row r="16" spans="1:255" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="112"/>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="105" t="s">
+      <c r="B16" s="110"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="94" t="s">
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="94"/>
-      <c r="M16" s="93" t="s">
+      <c r="L16" s="106"/>
+      <c r="M16" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="93"/>
+      <c r="N16" s="107"/>
       <c r="O16" s="47" t="s">
         <v>17</v>
       </c>
@@ -40030,8 +40217,8 @@
       <c r="F17" s="59"/>
       <c r="G17" s="70"/>
       <c r="H17" s="70"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="118"/>
       <c r="K17" s="6"/>
       <c r="L17" s="16"/>
       <c r="M17" s="71"/>
@@ -40289,8 +40476,8 @@
       <c r="F18" s="59"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="118"/>
       <c r="K18" s="6"/>
       <c r="L18" s="16"/>
       <c r="M18" s="71"/>
@@ -40799,18 +40986,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="63"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="7"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="95" t="s">
+      <c r="K20" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="95"/>
+      <c r="L20" s="100"/>
       <c r="M20" s="23"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
@@ -41068,8 +41255,8 @@
       <c r="H21" s="10"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="95"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
       <c r="M21" s="23"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
@@ -43424,8 +43611,25 @@
       <c r="D33" s="51"/>
     </row>
   </sheetData>
-  <autoFilter ref="K1:K33"/>
+  <autoFilter ref="K1:K33" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="33">
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B8:B9"/>
@@ -43442,45 +43646,28 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:K15">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17:K19">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K19" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G15 G17:G18" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$B$22:$B$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11:K15 K17:K18" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>$B$29:$B$31</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M11:M15 M17:M18" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>$B$26:$B$27</formula1>
     </dataValidation>
   </dataValidations>
